--- a/data/trans_orig/IP19C02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Edad-trans_orig.xlsx
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77666</t>
+          <t>77644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83429</t>
+          <t>83266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74722</t>
+          <t>74505</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79743</t>
+          <t>79739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154601</t>
+          <t>154783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162024</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>22509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87207</t>
+          <t>86599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95442</t>
+          <t>95316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91635</t>
+          <t>91404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100974</t>
+          <t>100835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181287</t>
+          <t>182403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194232</t>
+          <t>194940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140804</t>
+          <t>140677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153388</t>
+          <t>153405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154465</t>
+          <t>153811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165611</t>
+          <t>165314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300126</t>
+          <t>299564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315898</t>
+          <t>316601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>60805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317147</t>
+          <t>316268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332669</t>
+          <t>332424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>329036</t>
+          <t>329066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>344053</t>
+          <t>344419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651046</t>
+          <t>651856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>673269</t>
+          <t>672842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70364</t>
+          <t>70545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76250</t>
+          <t>76271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83125</t>
+          <t>83947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90828</t>
+          <t>91309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157613</t>
+          <t>157818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166068</t>
+          <t>166318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,47 +3416,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12149</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7425</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>18727</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12149</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7196</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>19240</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115406</t>
+          <t>115832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123049</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119075</t>
+          <t>118872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128269</t>
+          <t>128074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,47 +3529,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>245023</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>238445</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>249747</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,11%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>245023</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>237932</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>249976</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129073</t>
+          <t>128529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140195</t>
+          <t>140260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123377</t>
+          <t>123022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133709</t>
+          <t>133623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254346</t>
+          <t>256351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270878</t>
+          <t>271423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56189</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324298</t>
+          <t>325276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339465</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>333623</t>
+          <t>334305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349126</t>
+          <t>349312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>663057</t>
+          <t>665382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684994</t>
+          <t>684738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>23431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55262</t>
+          <t>54961</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68268</t>
+          <t>67969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77298</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126948</t>
+          <t>126758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139162</t>
+          <t>139156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35627</t>
+          <t>35244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>65667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113757</t>
+          <t>113571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128980</t>
+          <t>129332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113714</t>
+          <t>114097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129836</t>
+          <t>129958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233192</t>
+          <t>232591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255204</t>
+          <t>255831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45517</t>
+          <t>45795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57913</t>
+          <t>57347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81691</t>
+          <t>82099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102682</t>
+          <t>102590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118971</t>
+          <t>119021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106591</t>
+          <t>108297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198669</t>
+          <t>198261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>222447</t>
+          <t>223013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57080</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82128</t>
+          <t>81368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59392</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>86057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>124700</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159082</t>
+          <t>158533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280490</t>
+          <t>281250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305538</t>
+          <t>305772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>282358</t>
+          <t>281951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308616</t>
+          <t>307927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>571544</t>
+          <t>572093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>606668</t>
+          <t>605926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>32935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>51949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57288</t>
+          <t>57194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41456</t>
+          <t>41201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56485</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92086</t>
+          <t>91378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>110392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46519</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61001</t>
+          <t>59928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87331</t>
+          <t>87090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75384</t>
+          <t>76887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93352</t>
+          <t>94132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117452</t>
+          <t>118778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137373</t>
+          <t>137993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199360</t>
+          <t>199601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225690</t>
+          <t>226763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53497</t>
+          <t>53592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76686</t>
+          <t>76934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70257</t>
+          <t>70292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102158</t>
+          <t>102769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129501</t>
+          <t>130135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169810</t>
+          <t>170622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121051</t>
+          <t>120803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144240</t>
+          <t>144145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135050</t>
+          <t>134439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166951</t>
+          <t>166916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>265135</t>
+          <t>264323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305444</t>
+          <t>304810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100387</t>
+          <t>100101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133507</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132619</t>
+          <t>131763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173719</t>
+          <t>173549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242682</t>
+          <t>243120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295243</t>
+          <t>295973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258126</t>
+          <t>260403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291246</t>
+          <t>291532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>310725</t>
+          <t>310895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>351825</t>
+          <t>352681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>580833</t>
+          <t>580103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>633394</t>
+          <t>632956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5842</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2940</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6691</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2494</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5913</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77924</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74576</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>81395</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77644</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83266</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77901</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>83416</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>77924</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>74505</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>79739</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154783</t>
+          <t>154181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161980</t>
+          <t>162114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8706</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4946</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14064</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7256</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3877</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12594</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8706</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14315</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>97013</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>91655</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>100773</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>91937</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86599</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>95316</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87058</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>95424</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,69%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>97013</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>91404</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>100835</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182403</t>
+          <t>181881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194940</t>
+          <t>194170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12942</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8287</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19398</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15546</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10092</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22820</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10372</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22676</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12942</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8387</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19890</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37633</t>
+          <t>36643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>160759</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>154303</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>165414</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>147951</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140677</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153405</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>140821</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>153125</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>160759</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>153811</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>165314</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299564</t>
+          <t>300554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316601</t>
+          <t>316455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17335</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33220</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25741</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18506</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34662</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19209</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34955</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17312</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>32665</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>337590</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>328511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>344396</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>483</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>325189</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>316268</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>332424</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>315975</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>331721</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>337590</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>329066</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>344419</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651856</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>672842</t>
+          <t>672707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,107 +2670,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2622</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2671</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8714</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2578</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6396</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3454</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8117</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88610</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83350</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90835</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>74363</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>70545</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76271</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>70633</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>76267</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88610</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83947</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91309</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157818</t>
+          <t>157429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166318</t>
+          <t>166309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>76941</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>76941</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>76941</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7674</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13319</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4474</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1665</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9432</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,58%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7674</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13214</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>124412</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>118767</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128064</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>120612</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115832</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>123498</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>115654</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>123421</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,42%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>124412</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>118872</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>128074</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238445</t>
+          <t>238700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249747</t>
+          <t>250111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>12083</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7487</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18089</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>12682</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7660</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19391</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7627</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19066</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12083</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7560</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18161</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>33306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>129100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>123094</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133696</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>135238</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>128529</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>140260</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>128854</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>140293</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>129100</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>123022</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>133623</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256351</t>
+          <t>255797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>271423</t>
+          <t>271196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20361</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13830</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27968</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14207</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28582</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>16690</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31697</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>55641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>342791</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>333615</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>349314</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>332883</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>325276</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>339414</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>324662</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>339037</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>342791</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>334305</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>349312</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665382</t>
+          <t>663605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684738</t>
+          <t>685482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353244</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353244</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353244</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>8486</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4610</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13948</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>8060</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4520</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13099</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4406</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13211</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8486</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14160</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23431</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73643</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68181</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77519</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54961</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63540</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>54849</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>63654</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,16%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>73643</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>67969</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>77299</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126758</t>
+          <t>126496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139156</t>
+          <t>139216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26956</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19861</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35952</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>26921</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19585</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35346</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19799</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35039</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>26956</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19383</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>35244</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65667</t>
+          <t>66187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>122385</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>113389</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>129480</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>121996</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113571</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129332</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113878</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>129118</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>122385</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>114097</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>129958</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232591</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255831</t>
+          <t>254806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>36496</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28059</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45563</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>33797</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26084</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>42515</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>26474</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42764</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36496</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26958</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>45795</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57347</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82099</t>
+          <t>82989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98759</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89692</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>107196</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>111308</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>102590</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>119021</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102341</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>118631</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>76,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98759</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>89460</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>108297</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198261</t>
+          <t>197371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223013</t>
+          <t>221055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58586</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84759</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>68778</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>56846</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81368</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>57202</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>81714</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>71938</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>60081</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>86057</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>122953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158533</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>296070</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>283249</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>309422</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>426</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>293840</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>281250</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>305772</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>280904</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>305416</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>77,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>296070</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>281951</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>307927</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>572093</t>
+          <t>572469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>605926</t>
+          <t>607673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1698</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1847</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4134</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5232</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24292</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18099</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31667</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13705</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9002</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19855</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41450</t>
+          <t>38137</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32935</t>
+          <t>29625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51949</t>
+          <t>47453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43278</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35903</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49471</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52491</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46341</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>57194</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>49604</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41201</t>
+          <t>43794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56552</t>
+          <t>54730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>101877</t>
+          <t>92883</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91378</t>
+          <t>83567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110392</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37879</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28167</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48106</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36837</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27771</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45016</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>31402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>49045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72754</t>
+          <t>77466</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59928</t>
+          <t>65084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87090</t>
+          <t>91201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117419</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>107192</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127131</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>75,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>81,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>85066</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76887</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94132</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>69,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128871</t>
+          <t>82253</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118778</t>
+          <t>72795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137993</t>
+          <t>90438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>213937</t>
+          <t>199672</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199601</t>
+          <t>185937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226763</t>
+          <t>212054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91578</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>74823</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>108862</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>63949</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>53592</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>76934</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86914</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70292</t>
+          <t>55547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102769</t>
+          <t>80604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>150864</t>
+          <t>160477</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130135</t>
+          <t>140709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170622</t>
+          <t>182210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>141972</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124688</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>158727</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>133788</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>120803</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144145</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67,66%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>150294</t>
+          <t>136016</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134439</t>
+          <t>124312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166916</t>
+          <t>149369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>284081</t>
+          <t>277989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264323</t>
+          <t>256256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>304810</t>
+          <t>297757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>135027</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>174902</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>116339</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>131230</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131763</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173549</t>
+          <t>139724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>268849</t>
+          <t>279704</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243120</t>
+          <t>254485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295973</t>
+          <t>306859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>305648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>286193</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>326068</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>389</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>275294</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>260403</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>291532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>70,29%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>331934</t>
+          <t>272020</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>310895</t>
+          <t>256554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352681</t>
+          <t>290169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>607227</t>
+          <t>577668</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>580103</t>
+          <t>550513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>632956</t>
+          <t>602887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
